--- a/thread-strength/02_data/thread-summary-trossulus-clean.xlsx
+++ b/thread-strength/02_data/thread-summary-trossulus-clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattg\Desktop\github\PSMFC-mytilus-byssus-pilot\thread-strength\02_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF5891-930B-4B11-A31B-ACC41DBA777A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6115B3-C9E4-4B62-8EA4-B7DC2E108E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,29 +3378,29 @@
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G49" t="s">
         <v>65</v>
       </c>
       <c r="H49">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="I49">
-        <v>0.24552306448818501</v>
+        <v>4.7829439808670798E-2</v>
       </c>
       <c r="J49">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="K49">
         <f>H49/J49*1000</f>
-        <v>133.72093023255815</v>
+        <v>32.051282051282058</v>
       </c>
       <c r="L49" t="s">
         <v>25</v>
@@ -3420,29 +3420,29 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
         <v>65</v>
       </c>
       <c r="H50">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="I50">
-        <v>4.7829439808670798E-2</v>
+        <v>0.24552306448818501</v>
       </c>
       <c r="J50">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="K50">
         <f>H50/J50*1000</f>
-        <v>32.051282051282058</v>
+        <v>133.72093023255815</v>
       </c>
       <c r="L50" t="s">
         <v>25</v>
@@ -3840,29 +3840,29 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G60" t="s">
         <v>65</v>
       </c>
       <c r="H60">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I60">
-        <v>0.37068239291806698</v>
+        <v>5.4917041087909201E-2</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="K60">
         <f>H60/J60*1000</f>
-        <v>85</v>
+        <v>61.728395061728392</v>
       </c>
       <c r="L60" t="s">
         <v>17</v>
@@ -3882,29 +3882,29 @@
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
         <v>65</v>
       </c>
       <c r="H61">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="I61">
-        <v>5.4917041087909201E-2</v>
+        <v>0.37068239291806698</v>
       </c>
       <c r="J61">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="K61">
         <f>H61/J61*1000</f>
-        <v>61.728395061728392</v>
+        <v>85</v>
       </c>
       <c r="L61" t="s">
         <v>17</v>
@@ -4386,32 +4386,32 @@
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G73" t="s">
         <v>65</v>
       </c>
       <c r="H73">
-        <v>0.51</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="I73">
-        <v>2.0000411926924802</v>
+        <v>0.216389235135135</v>
       </c>
       <c r="J73">
-        <v>4.54</v>
+        <v>3.25</v>
       </c>
       <c r="K73">
         <f>H73/J73*1000</f>
-        <v>112.33480176211454</v>
+        <v>69.230769230769241</v>
       </c>
       <c r="L73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M73" t="s">
         <v>18</v>
@@ -4428,32 +4428,32 @@
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
         <v>65</v>
       </c>
       <c r="H74">
-        <v>0.22500000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="I74">
-        <v>0.216389235135135</v>
+        <v>2.0000411926924802</v>
       </c>
       <c r="J74">
-        <v>3.25</v>
+        <v>4.54</v>
       </c>
       <c r="K74">
         <f>H74/J74*1000</f>
-        <v>69.230769230769241</v>
+        <v>112.33480176211454</v>
       </c>
       <c r="L74" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M74" t="s">
         <v>18</v>
@@ -4470,32 +4470,32 @@
         <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
         <v>65</v>
       </c>
       <c r="H75">
-        <v>0.45</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="I75">
-        <v>1.6923572166482399</v>
+        <v>0.79349665565729199</v>
       </c>
       <c r="J75">
-        <v>3.85</v>
+        <v>3.39</v>
       </c>
       <c r="K75">
         <f>H75/J75*1000</f>
-        <v>116.88311688311688</v>
+        <v>98.820058997050154</v>
       </c>
       <c r="L75" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M75" t="s">
         <v>18</v>
@@ -4512,32 +4512,32 @@
         <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G76" t="s">
         <v>65</v>
       </c>
       <c r="H76">
-        <v>0.33500000000000002</v>
+        <v>0.45</v>
       </c>
       <c r="I76">
-        <v>0.79349665565729199</v>
+        <v>1.6923572166482399</v>
       </c>
       <c r="J76">
-        <v>3.39</v>
+        <v>3.85</v>
       </c>
       <c r="K76">
         <f>H76/J76*1000</f>
-        <v>98.820058997050154</v>
+        <v>116.88311688311688</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M76" t="s">
         <v>18</v>
@@ -4554,32 +4554,32 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G77" t="s">
         <v>65</v>
       </c>
       <c r="H77">
-        <v>0.20499999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="I77">
-        <v>0.21042009292210101</v>
+        <v>8.0756167488511804E-2</v>
       </c>
       <c r="J77">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="K77">
         <f>H77/J77*1000</f>
-        <v>61.011904761904759</v>
+        <v>36.858974358974358</v>
       </c>
       <c r="L77" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M77" t="s">
         <v>18</v>
@@ -4596,32 +4596,32 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G78" t="s">
         <v>65</v>
       </c>
       <c r="H78">
-        <v>0.115</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="I78">
-        <v>8.0756167488511804E-2</v>
+        <v>0.21042009292210101</v>
       </c>
       <c r="J78">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="K78">
         <f>H78/J78*1000</f>
-        <v>36.858974358974358</v>
+        <v>61.011904761904759</v>
       </c>
       <c r="L78" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
         <v>18</v>
@@ -4848,32 +4848,32 @@
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G84" t="s">
         <v>65</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="I84">
-        <v>0.34880586604226299</v>
+        <v>0.28805482522275</v>
       </c>
       <c r="J84">
-        <v>3.79</v>
+        <v>3.11</v>
       </c>
       <c r="K84">
         <f>H84/J84*1000</f>
-        <v>79.155672823218993</v>
+        <v>70.739549839228303</v>
       </c>
       <c r="L84" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M84" t="s">
         <v>18</v>
@@ -4890,32 +4890,32 @@
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E85" t="s">
         <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G85" t="s">
         <v>65</v>
       </c>
       <c r="H85">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="I85">
-        <v>0.28805482522275</v>
+        <v>0.34880586604226299</v>
       </c>
       <c r="J85">
-        <v>3.11</v>
+        <v>3.79</v>
       </c>
       <c r="K85">
         <f>H85/J85*1000</f>
-        <v>70.739549839228303</v>
+        <v>79.155672823218993</v>
       </c>
       <c r="L85" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s">
         <v>18</v>
@@ -4932,32 +4932,32 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G86" t="s">
         <v>65</v>
       </c>
       <c r="H86">
-        <v>0.26</v>
+        <v>0.155</v>
       </c>
       <c r="I86">
-        <v>0.49293459906151199</v>
+        <v>5.4188989450119802E-2</v>
       </c>
       <c r="J86">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="K86">
         <f>H86/J86*1000</f>
-        <v>107.43801652892563</v>
+        <v>65.12605042016807</v>
       </c>
       <c r="L86" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M86" t="s">
         <v>18</v>
@@ -4974,32 +4974,32 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
         <v>65</v>
       </c>
       <c r="H87">
-        <v>0.155</v>
+        <v>0.26</v>
       </c>
       <c r="I87">
-        <v>5.4188989450119802E-2</v>
+        <v>0.49293459906151199</v>
       </c>
       <c r="J87">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="K87">
         <f>H87/J87*1000</f>
-        <v>65.12605042016807</v>
+        <v>107.43801652892563</v>
       </c>
       <c r="L87" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M87" t="s">
         <v>18</v>
@@ -5016,32 +5016,32 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
         <v>65</v>
       </c>
       <c r="H88">
-        <v>0.19500000000000001</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="I88">
-        <v>0.105241345371119</v>
+        <v>0.10148659852088</v>
       </c>
       <c r="J88">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="K88">
         <f>H88/J88*1000</f>
-        <v>47.33009708737864</v>
+        <v>40.845070422535215</v>
       </c>
       <c r="L88" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M88" t="s">
         <v>18</v>
@@ -5058,32 +5058,32 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G89" t="s">
         <v>65</v>
       </c>
       <c r="H89">
-        <v>0.14499999999999999</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="I89">
-        <v>0.10148659852088</v>
+        <v>0.105241345371119</v>
       </c>
       <c r="J89">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="K89">
         <f>H89/J89*1000</f>
-        <v>40.845070422535215</v>
+        <v>47.33009708737864</v>
       </c>
       <c r="L89" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M89" t="s">
         <v>18</v>
@@ -5100,32 +5100,32 @@
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G90" t="s">
         <v>65</v>
       </c>
       <c r="H90">
-        <v>0.14000000000000001</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I90">
-        <v>8.4310382573428003E-2</v>
+        <v>8.7149927795955803E-2</v>
       </c>
       <c r="J90">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="K90">
         <f>H90/J90*1000</f>
-        <v>48.611111111111121</v>
+        <v>41.935483870967744</v>
       </c>
       <c r="L90" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M90" t="s">
         <v>18</v>
@@ -5142,32 +5142,32 @@
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
         <v>65</v>
       </c>
       <c r="H91">
-        <v>6.5000000000000002E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I91">
-        <v>8.7149927795955803E-2</v>
+        <v>8.4310382573428003E-2</v>
       </c>
       <c r="J91">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="K91">
         <f>H91/J91*1000</f>
-        <v>41.935483870967744</v>
+        <v>48.611111111111121</v>
       </c>
       <c r="L91" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M91" t="s">
         <v>18</v>
@@ -5184,32 +5184,32 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
         <v>65</v>
       </c>
       <c r="H92">
-        <v>0.125</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I92">
-        <v>0.12329344585987299</v>
+        <v>3.50850902805546E-2</v>
       </c>
       <c r="J92">
-        <v>4.13</v>
+        <v>2.91</v>
       </c>
       <c r="K92">
         <f>H92/J92*1000</f>
-        <v>30.26634382566586</v>
+        <v>24.054982817869416</v>
       </c>
       <c r="L92" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M92" t="s">
         <v>18</v>
@@ -5226,32 +5226,32 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G93" t="s">
         <v>65</v>
       </c>
       <c r="H93">
-        <v>7.0000000000000007E-2</v>
+        <v>0.125</v>
       </c>
       <c r="I93">
-        <v>3.50850902805546E-2</v>
+        <v>0.12329344585987299</v>
       </c>
       <c r="J93">
-        <v>2.91</v>
+        <v>4.13</v>
       </c>
       <c r="K93">
         <f>H93/J93*1000</f>
-        <v>24.054982817869416</v>
+        <v>30.26634382566586</v>
       </c>
       <c r="L93" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M93" t="s">
         <v>18</v>
@@ -5352,32 +5352,32 @@
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G96" t="s">
         <v>65</v>
       </c>
       <c r="H96">
-        <v>0.185</v>
+        <v>0.08</v>
       </c>
       <c r="I96">
-        <v>0.245195530451986</v>
+        <v>0.118069319815112</v>
       </c>
       <c r="J96">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="K96">
         <f>H96/J96*1000</f>
-        <v>74</v>
+        <v>48.484848484848492</v>
       </c>
       <c r="L96" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M96" t="s">
         <v>18</v>
@@ -5394,32 +5394,32 @@
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G97" t="s">
         <v>65</v>
       </c>
       <c r="H97">
-        <v>0.08</v>
+        <v>0.185</v>
       </c>
       <c r="I97">
-        <v>0.118069319815112</v>
+        <v>0.245195530451986</v>
       </c>
       <c r="J97">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="K97">
         <f>H97/J97*1000</f>
-        <v>48.484848484848492</v>
+        <v>74</v>
       </c>
       <c r="L97" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M97" t="s">
         <v>18</v>
@@ -5538,11 +5538,11 @@
         <v>0.16982813029158</v>
       </c>
       <c r="J100">
-        <v>3.58</v>
+        <v>2.58</v>
       </c>
       <c r="K100">
         <f>H100/J100*1000</f>
-        <v>51.675977653631286</v>
+        <v>71.705426356589143</v>
       </c>
       <c r="L100" t="s">
         <v>17</v>
@@ -5730,32 +5730,32 @@
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G105" t="s">
         <v>123</v>
       </c>
       <c r="H105">
-        <v>0.27</v>
+        <v>0.105</v>
       </c>
       <c r="I105">
-        <v>0.51989839090909096</v>
+        <v>0.11081432197713401</v>
       </c>
       <c r="J105">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="K105">
         <f>H105/J105*1000</f>
-        <v>71.052631578947384</v>
+        <v>29.914529914529915</v>
       </c>
       <c r="L105" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M105" t="s">
         <v>18</v>
@@ -5772,32 +5772,32 @@
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
         <v>16</v>
       </c>
       <c r="F106" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
         <v>123</v>
       </c>
       <c r="H106">
-        <v>0.105</v>
+        <v>0.27</v>
       </c>
       <c r="I106">
-        <v>0.11081432197713401</v>
+        <v>0.51989839090909096</v>
       </c>
       <c r="J106">
-        <v>3.51</v>
+        <v>3.8</v>
       </c>
       <c r="K106">
         <f>H106/J106*1000</f>
-        <v>29.914529914529915</v>
+        <v>71.052631578947384</v>
       </c>
       <c r="L106" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M106" t="s">
         <v>18</v>
@@ -5874,11 +5874,11 @@
         <v>1.70848243847461</v>
       </c>
       <c r="J108">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="K108">
         <f>H108/J108*1000</f>
-        <v>260.5263157894737</v>
+        <v>141.42857142857144</v>
       </c>
       <c r="L108" t="s">
         <v>21</v>
@@ -6276,29 +6276,29 @@
         <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
       </c>
       <c r="F118" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G118" t="s">
         <v>123</v>
       </c>
       <c r="H118">
-        <v>0.32500000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="I118">
-        <v>1.2473135066516401</v>
+        <v>8.1459075862069005E-2</v>
       </c>
       <c r="J118">
-        <v>5.18</v>
+        <v>3.96</v>
       </c>
       <c r="K118">
         <f>H118/J118*1000</f>
-        <v>62.74131274131274</v>
+        <v>29.040404040404045</v>
       </c>
       <c r="L118" t="s">
         <v>25</v>
@@ -6318,29 +6318,29 @@
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G119" t="s">
         <v>123</v>
       </c>
       <c r="H119">
-        <v>0.115</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="I119">
-        <v>8.1459075862069005E-2</v>
+        <v>1.2473135066516401</v>
       </c>
       <c r="J119">
-        <v>3.96</v>
+        <v>5.18</v>
       </c>
       <c r="K119">
         <f>H119/J119*1000</f>
-        <v>29.040404040404045</v>
+        <v>62.74131274131274</v>
       </c>
       <c r="L119" t="s">
         <v>25</v>
@@ -6528,29 +6528,29 @@
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G124" t="s">
         <v>123</v>
       </c>
       <c r="H124">
-        <v>0.36499999999999999</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="I124">
-        <v>0.55860881749949498</v>
+        <v>0.16691093120964101</v>
       </c>
       <c r="J124">
-        <v>4.8499999999999996</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="K124">
         <f>H124/J124*1000</f>
-        <v>75.257731958762903</v>
+        <v>30.133928571428573</v>
       </c>
       <c r="L124" t="s">
         <v>17</v>
@@ -6570,29 +6570,29 @@
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G125" t="s">
         <v>123</v>
       </c>
       <c r="H125">
-        <v>0.13500000000000001</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="I125">
-        <v>0.16691093120964101</v>
+        <v>0.55860881749949498</v>
       </c>
       <c r="J125">
-        <v>4.4800000000000004</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="K125">
         <f>H125/J125*1000</f>
-        <v>30.133928571428573</v>
+        <v>75.257731958762903</v>
       </c>
       <c r="L125" t="s">
         <v>17</v>
@@ -6654,32 +6654,32 @@
         <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
       </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G127" t="s">
         <v>123</v>
       </c>
       <c r="H127">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="I127">
-        <v>0.39858684322429899</v>
+        <v>0.14517854052252899</v>
       </c>
       <c r="J127">
-        <v>4.47</v>
+        <v>3</v>
       </c>
       <c r="K127">
         <f>H127/J127*1000</f>
-        <v>67.114093959731548</v>
+        <v>60</v>
       </c>
       <c r="L127" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M127" t="s">
         <v>18</v>
@@ -6696,32 +6696,32 @@
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G128" t="s">
         <v>123</v>
       </c>
       <c r="H128">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="I128">
-        <v>0.14517854052252899</v>
+        <v>0.39858684322429899</v>
       </c>
       <c r="J128">
-        <v>3</v>
+        <v>4.47</v>
       </c>
       <c r="K128">
         <f>H128/J128*1000</f>
-        <v>60</v>
+        <v>67.114093959731548</v>
       </c>
       <c r="L128" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M128" t="s">
         <v>18</v>
@@ -6738,32 +6738,32 @@
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G129" t="s">
         <v>123</v>
       </c>
       <c r="H129">
-        <v>0.23499999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="I129">
-        <v>0.348496204103527</v>
+        <v>0.16669796109842899</v>
       </c>
       <c r="J129">
-        <v>3.85</v>
+        <v>3.09</v>
       </c>
       <c r="K129">
         <f>H129/J129*1000</f>
-        <v>61.038961038961034</v>
+        <v>33.980582524271846</v>
       </c>
       <c r="L129" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M129" t="s">
         <v>18</v>
@@ -6780,32 +6780,32 @@
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G130" t="s">
         <v>123</v>
       </c>
       <c r="H130">
-        <v>0.105</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="I130">
-        <v>0.16669796109842899</v>
+        <v>0.348496204103527</v>
       </c>
       <c r="J130">
-        <v>3.09</v>
+        <v>3.85</v>
       </c>
       <c r="K130">
         <f>H130/J130*1000</f>
-        <v>33.980582524271846</v>
+        <v>61.038961038961034</v>
       </c>
       <c r="L130" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M130" t="s">
         <v>18</v>
@@ -6990,29 +6990,29 @@
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
         <v>123</v>
       </c>
       <c r="H135">
-        <v>0.23499999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="I135">
-        <v>0.30540731641990998</v>
+        <v>7.6178772284288598E-2</v>
       </c>
       <c r="J135">
-        <v>4.1100000000000003</v>
+        <v>4.05</v>
       </c>
       <c r="K135">
         <f>H135/J135*1000</f>
-        <v>57.177615571776151</v>
+        <v>24.691358024691361</v>
       </c>
       <c r="L135" t="s">
         <v>17</v>
@@ -7032,29 +7032,29 @@
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
         <v>16</v>
       </c>
       <c r="F136" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G136" t="s">
         <v>123</v>
       </c>
       <c r="H136">
-        <v>0.1</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="I136">
-        <v>7.6178772284288598E-2</v>
+        <v>0.30540731641990998</v>
       </c>
       <c r="J136">
-        <v>4.05</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="K136">
         <f>H136/J136*1000</f>
-        <v>24.691358024691361</v>
+        <v>57.177615571776151</v>
       </c>
       <c r="L136" t="s">
         <v>17</v>
@@ -7074,32 +7074,32 @@
         <v>2</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E137" t="s">
         <v>16</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G137" t="s">
         <v>123</v>
       </c>
       <c r="H137">
-        <v>0.6</v>
+        <v>0.215</v>
       </c>
       <c r="I137">
-        <v>1.2276633373936401</v>
+        <v>0.30211758492419899</v>
       </c>
       <c r="J137">
-        <v>5.96</v>
+        <v>3.7</v>
       </c>
       <c r="K137">
         <f>H137/J137*1000</f>
-        <v>100.67114093959731</v>
+        <v>58.108108108108105</v>
       </c>
       <c r="L137" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M137" t="s">
         <v>18</v>
@@ -7116,32 +7116,32 @@
         <v>2</v>
       </c>
       <c r="D138" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E138" t="s">
         <v>16</v>
       </c>
       <c r="F138" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G138" t="s">
         <v>123</v>
       </c>
       <c r="H138">
-        <v>0.215</v>
+        <v>0.6</v>
       </c>
       <c r="I138">
-        <v>0.30211758492419899</v>
+        <v>1.2276633373936401</v>
       </c>
       <c r="J138">
-        <v>3.7</v>
+        <v>5.96</v>
       </c>
       <c r="K138">
         <f>H138/J138*1000</f>
-        <v>58.108108108108105</v>
+        <v>100.67114093959731</v>
       </c>
       <c r="L138" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M138" t="s">
         <v>18</v>
@@ -7302,11 +7302,11 @@
         <v>0.37284461702725802</v>
       </c>
       <c r="J142">
-        <v>1.31</v>
+        <v>2.31</v>
       </c>
       <c r="K142">
         <f>H142/J142*1000</f>
-        <v>255.72519083969465</v>
+        <v>145.02164502164501</v>
       </c>
       <c r="L142" t="s">
         <v>25</v>
@@ -7326,32 +7326,32 @@
         <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E143" t="s">
         <v>16</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G143" t="s">
         <v>123</v>
       </c>
       <c r="H143">
-        <v>0.28999999999999998</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I143">
-        <v>0.46596396635110798</v>
+        <v>1.4716209660355299E-2</v>
       </c>
       <c r="J143">
-        <v>2.4900000000000002</v>
+        <v>2.42</v>
       </c>
       <c r="K143">
         <f>H143/J143*1000</f>
-        <v>116.46586345381523</v>
+        <v>10.330578512396695</v>
       </c>
       <c r="L143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M143" t="s">
         <v>18</v>
@@ -7368,32 +7368,32 @@
         <v>2</v>
       </c>
       <c r="D144" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E144" t="s">
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G144" t="s">
         <v>123</v>
       </c>
       <c r="H144">
-        <v>2.5000000000000001E-2</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I144">
-        <v>1.4716209660355299E-2</v>
+        <v>0.46596396635110798</v>
       </c>
       <c r="J144">
-        <v>1.42</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="K144">
         <f>H144/J144*1000</f>
-        <v>17.605633802816904</v>
+        <v>116.46586345381523</v>
       </c>
       <c r="L144" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M144" t="s">
         <v>18</v>
@@ -7956,29 +7956,29 @@
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E158" t="s">
         <v>16</v>
       </c>
       <c r="F158" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G158" t="s">
         <v>123</v>
       </c>
       <c r="H158">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="I158">
-        <v>8.7767037820436197E-2</v>
+        <v>0.17601997734137101</v>
       </c>
       <c r="J158">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="K158">
         <f>H158/J158*1000</f>
-        <v>41.946308724832214</v>
+        <v>41.237113402061858</v>
       </c>
       <c r="L158" t="s">
         <v>17</v>
@@ -7998,29 +7998,29 @@
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G159" t="s">
         <v>123</v>
       </c>
       <c r="H159">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="I159">
-        <v>0.17601997734137101</v>
+        <v>8.7767037820436197E-2</v>
       </c>
       <c r="J159">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="K159">
         <f>H159/J159*1000</f>
-        <v>41.237113402061858</v>
+        <v>41.946308724832214</v>
       </c>
       <c r="L159" t="s">
         <v>17</v>
@@ -8124,32 +8124,32 @@
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G162" t="s">
         <v>123</v>
       </c>
       <c r="H162">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="I162">
-        <v>1.1487642120294801</v>
+        <v>7.7264101835848101E-2</v>
       </c>
       <c r="J162">
-        <v>4.12</v>
+        <v>1.37</v>
       </c>
       <c r="K162">
         <f>H162/J162*1000</f>
-        <v>89.805825242718441</v>
+        <v>36.496350364963497</v>
       </c>
       <c r="L162" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M162" t="s">
         <v>18</v>
@@ -8166,32 +8166,32 @@
         <v>3</v>
       </c>
       <c r="D163" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s">
         <v>16</v>
       </c>
       <c r="F163" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G163" t="s">
         <v>123</v>
       </c>
       <c r="H163">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="I163">
-        <v>7.7264101835848101E-2</v>
+        <v>1.1487642120294801</v>
       </c>
       <c r="J163">
-        <v>1.37</v>
+        <v>4.12</v>
       </c>
       <c r="K163">
         <f>H163/J163*1000</f>
-        <v>36.496350364963497</v>
+        <v>89.805825242718441</v>
       </c>
       <c r="L163" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M163" t="s">
         <v>18</v>
@@ -8208,32 +8208,32 @@
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
         <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G164" t="s">
         <v>123</v>
       </c>
       <c r="H164">
-        <v>0.24</v>
+        <v>0.155</v>
       </c>
       <c r="I164">
-        <v>0.70642270065373602</v>
+        <v>0.15447235761446801</v>
       </c>
       <c r="J164">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="K164">
         <f>H164/J164*1000</f>
-        <v>136.36363636363635</v>
+        <v>91.715976331360949</v>
       </c>
       <c r="L164" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M164" t="s">
         <v>18</v>
@@ -8250,32 +8250,32 @@
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E165" t="s">
         <v>16</v>
       </c>
       <c r="F165" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="G165" t="s">
         <v>123</v>
       </c>
       <c r="H165">
-        <v>0.155</v>
+        <v>0.24</v>
       </c>
       <c r="I165">
-        <v>0.15447235761446801</v>
+        <v>0.70642270065373602</v>
       </c>
       <c r="J165">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="K165">
         <f>H165/J165*1000</f>
-        <v>91.715976331360949</v>
+        <v>136.36363636363635</v>
       </c>
       <c r="L165" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M165" t="s">
         <v>18</v>
@@ -8394,11 +8394,11 @@
         <v>1.0737792529743999</v>
       </c>
       <c r="J168">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="K168">
         <f>H168/J168*1000</f>
-        <v>204.91803278688525</v>
+        <v>132.50883392226149</v>
       </c>
       <c r="L168" t="s">
         <v>25</v>
@@ -9006,32 +9006,32 @@
         <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
       </c>
       <c r="F183" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G183" t="s">
         <v>183</v>
       </c>
       <c r="H183">
-        <v>0.38</v>
+        <v>0.125</v>
       </c>
       <c r="I183">
-        <v>0.73072930564971805</v>
+        <v>0.13747225759058099</v>
       </c>
       <c r="J183">
-        <v>3.71</v>
+        <v>1.75</v>
       </c>
       <c r="K183">
         <f>H183/J183*1000</f>
-        <v>102.42587601078168</v>
+        <v>71.428571428571431</v>
       </c>
       <c r="L183" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M183" t="s">
         <v>18</v>
@@ -9048,32 +9048,32 @@
         <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
       </c>
       <c r="F184" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G184" t="s">
         <v>183</v>
       </c>
       <c r="H184">
-        <v>0.125</v>
+        <v>0.38</v>
       </c>
       <c r="I184">
-        <v>0.13747225759058099</v>
+        <v>0.73072930564971805</v>
       </c>
       <c r="J184">
-        <v>1.75</v>
+        <v>3.71</v>
       </c>
       <c r="K184">
         <f>H184/J184*1000</f>
-        <v>71.428571428571431</v>
+        <v>102.42587601078168</v>
       </c>
       <c r="L184" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M184" t="s">
         <v>18</v>
@@ -9174,29 +9174,29 @@
         <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
       </c>
       <c r="F187" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G187" t="s">
         <v>183</v>
       </c>
       <c r="H187">
-        <v>0.245</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I187">
-        <v>0.642948030883435</v>
+        <v>5.66006806165925E-2</v>
       </c>
       <c r="J187">
-        <v>4.63</v>
+        <v>1.43</v>
       </c>
       <c r="K187">
         <f>H187/J187*1000</f>
-        <v>52.915766738660906</v>
+        <v>48.951048951048961</v>
       </c>
       <c r="L187" t="s">
         <v>17</v>
@@ -9216,29 +9216,29 @@
         <v>2</v>
       </c>
       <c r="D188" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s">
         <v>16</v>
       </c>
       <c r="F188" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G188" t="s">
         <v>183</v>
       </c>
       <c r="H188">
-        <v>7.0000000000000007E-2</v>
+        <v>0.245</v>
       </c>
       <c r="I188">
-        <v>5.66006806165925E-2</v>
+        <v>0.642948030883435</v>
       </c>
       <c r="J188">
-        <v>1.43</v>
+        <v>4.63</v>
       </c>
       <c r="K188">
         <f>H188/J188*1000</f>
-        <v>48.951048951048961</v>
+        <v>52.915766738660906</v>
       </c>
       <c r="L188" t="s">
         <v>17</v>
@@ -9258,32 +9258,32 @@
         <v>3</v>
       </c>
       <c r="D189" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E189" t="s">
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G189" t="s">
         <v>183</v>
       </c>
       <c r="H189">
-        <v>0.375</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I189">
-        <v>1.4248593072770099</v>
+        <v>4.8402458127208399E-2</v>
       </c>
       <c r="J189">
-        <v>5.0199999999999996</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="K189">
         <f>H189/J189*1000</f>
-        <v>74.701195219123505</v>
+        <v>57.017543859649123</v>
       </c>
       <c r="L189" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M189" t="s">
         <v>18</v>
@@ -9300,32 +9300,32 @@
         <v>3</v>
       </c>
       <c r="D190" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E190" t="s">
         <v>16</v>
       </c>
       <c r="F190" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G190" t="s">
         <v>183</v>
       </c>
       <c r="H190">
-        <v>6.5000000000000002E-2</v>
+        <v>0.375</v>
       </c>
       <c r="I190">
-        <v>4.8402458127208399E-2</v>
+        <v>1.4248593072770099</v>
       </c>
       <c r="J190">
-        <v>1.1399999999999999</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="K190">
         <f>H190/J190*1000</f>
-        <v>57.017543859649123</v>
+        <v>74.701195219123505</v>
       </c>
       <c r="L190" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M190" t="s">
         <v>18</v>
@@ -9594,29 +9594,29 @@
         <v>3</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
         <v>16</v>
       </c>
       <c r="F197" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G197" t="s">
         <v>183</v>
       </c>
       <c r="H197">
-        <v>0.13</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I197">
-        <v>0.15739060844311201</v>
+        <v>7.6802706189629394E-2</v>
       </c>
       <c r="J197">
-        <v>4.03</v>
+        <v>2.99</v>
       </c>
       <c r="K197">
         <f>H197/J197*1000</f>
-        <v>32.258064516129032</v>
+        <v>25.083612040133776</v>
       </c>
       <c r="L197" t="s">
         <v>17</v>
@@ -9636,29 +9636,29 @@
         <v>3</v>
       </c>
       <c r="D198" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E198" t="s">
         <v>16</v>
       </c>
       <c r="F198" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G198" t="s">
         <v>183</v>
       </c>
       <c r="H198">
-        <v>7.4999999999999997E-2</v>
+        <v>0.13</v>
       </c>
       <c r="I198">
-        <v>7.6802706189629394E-2</v>
+        <v>0.15739060844311201</v>
       </c>
       <c r="J198">
-        <v>2.99</v>
+        <v>4.03</v>
       </c>
       <c r="K198">
         <f>H198/J198*1000</f>
-        <v>25.083612040133776</v>
+        <v>32.258064516129032</v>
       </c>
       <c r="L198" t="s">
         <v>17</v>
@@ -9846,32 +9846,32 @@
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E203" t="s">
         <v>16</v>
       </c>
       <c r="F203" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G203" t="s">
         <v>183</v>
       </c>
       <c r="H203">
-        <v>0.46500000000000002</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I203">
-        <v>1.05138779714286</v>
+        <v>4.2540095841646301E-2</v>
       </c>
       <c r="J203">
-        <v>4.7300000000000004</v>
+        <v>2.42</v>
       </c>
       <c r="K203">
         <f>H203/J203*1000</f>
-        <v>98.308668076109939</v>
+        <v>14.462809917355374</v>
       </c>
       <c r="L203" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M203" t="s">
         <v>18</v>
@@ -9888,32 +9888,32 @@
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
         <v>16</v>
       </c>
       <c r="F204" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G204" t="s">
         <v>183</v>
       </c>
       <c r="H204">
-        <v>3.5000000000000003E-2</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="I204">
-        <v>4.2540095841646301E-2</v>
+        <v>1.05138779714286</v>
       </c>
       <c r="J204">
-        <v>2.42</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="K204">
         <f>H204/J204*1000</f>
-        <v>14.462809917355374</v>
+        <v>98.308668076109939</v>
       </c>
       <c r="L204" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M204" t="s">
         <v>18</v>
@@ -10389,32 +10389,32 @@
         <v>2</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E216" t="s">
         <v>16</v>
       </c>
       <c r="F216" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G216" t="s">
         <v>183</v>
       </c>
       <c r="H216">
-        <v>0.34</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="I216">
-        <v>0.82855541944615496</v>
+        <v>0.27156342661190802</v>
       </c>
       <c r="J216">
-        <v>5.12</v>
+        <v>2.84</v>
       </c>
       <c r="K216">
         <f>H216/J216*1000</f>
-        <v>66.40625</v>
+        <v>61.619718309859159</v>
       </c>
       <c r="L216" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M216" t="s">
         <v>18</v>
@@ -10431,32 +10431,32 @@
         <v>2</v>
       </c>
       <c r="D217" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E217" t="s">
         <v>16</v>
       </c>
       <c r="F217" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G217" t="s">
         <v>183</v>
       </c>
       <c r="H217">
-        <v>0.17499999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="I217">
-        <v>0.27156342661190802</v>
+        <v>0.82855541944615496</v>
       </c>
       <c r="J217">
-        <v>2.84</v>
+        <v>5.12</v>
       </c>
       <c r="K217">
         <f>H217/J217*1000</f>
-        <v>61.619718309859159</v>
+        <v>66.40625</v>
       </c>
       <c r="L217" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M217" t="s">
         <v>18</v>
@@ -10641,32 +10641,32 @@
         <v>3</v>
       </c>
       <c r="D222" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E222" t="s">
         <v>16</v>
       </c>
       <c r="F222" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G222" t="s">
         <v>183</v>
       </c>
       <c r="H222">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="I222">
-        <v>0.336737629252917</v>
+        <v>0.105296621314472</v>
       </c>
       <c r="J222">
-        <v>3.71</v>
+        <v>3.21</v>
       </c>
       <c r="K222">
         <f>H222/J222*1000</f>
-        <v>67.385444743935309</v>
+        <v>37.383177570093459</v>
       </c>
       <c r="L222" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M222" t="s">
         <v>18</v>
@@ -10683,32 +10683,32 @@
         <v>3</v>
       </c>
       <c r="D223" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
         <v>16</v>
       </c>
       <c r="F223" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="G223" t="s">
         <v>183</v>
       </c>
       <c r="H223">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="I223">
-        <v>0.105296621314472</v>
+        <v>0.336737629252917</v>
       </c>
       <c r="J223">
-        <v>3.21</v>
+        <v>3.71</v>
       </c>
       <c r="K223">
         <f>H223/J223*1000</f>
-        <v>37.383177570093459</v>
+        <v>67.385444743935309</v>
       </c>
       <c r="L223" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M223" t="s">
         <v>18</v>
@@ -12669,7 +12669,7 @@
         <v>183</v>
       </c>
       <c r="H270">
-        <v>0.26500000000000001</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="I270">
         <v>0.282237984330381</v>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="K270">
         <f>H270/J270*1000</f>
-        <v>173.20261437908496</v>
+        <v>16.993464052287582</v>
       </c>
       <c r="L270" t="s">
         <v>25</v>
@@ -13949,9 +13949,9 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M302">
-    <sortCondition ref="B2:B302"/>
-    <sortCondition ref="C2:C302"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M307">
+    <sortCondition ref="B2:B307"/>
+    <sortCondition ref="A2:A307"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
